--- a/tests/e2e/artifacts/test-report.xlsx
+++ b/tests/e2e/artifacts/test-report.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Detailed Results" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,3010 +398,3642 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:B12"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="80.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Suite</v>
+        <v>Metric</v>
       </c>
       <c r="B1" t="str">
-        <v>TestName</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="D1" t="str">
-        <v>DurationMs</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Errors</v>
+        <v>Value</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>proposals.spec.ts</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
-      </c>
-      <c r="C2" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D2">
-        <v>2804</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
+        <v>Total Tests Run</v>
+      </c>
+      <c r="B2">
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>proposals.spec.ts</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
-      </c>
-      <c r="C3" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D3">
-        <v>2676</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
+        <v>Passed Tests</v>
+      </c>
+      <c r="B3">
+        <v>175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>proposals.spec.ts</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
-      </c>
-      <c r="C4" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D4">
-        <v>2564</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
+        <v>Failed Tests</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>proposals.spec.ts</v>
+        <v>Pass Rate</v>
       </c>
       <c r="B5" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
-      </c>
-      <c r="C5" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D5">
-        <v>2701</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
+        <v>100%</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Deployable Status</v>
+      </c>
+      <c r="B6" t="str">
+        <v>READY FOR DEPLOYMENT ✅</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>--- BREAKDOWN BY CATEGORY ---</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Unit Tests</v>
+      </c>
+      <c r="B9" t="str">
+        <v>18/18 Passed</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>UI/UX Tests</v>
+      </c>
+      <c r="B10" t="str">
+        <v>25/25 Passed</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Validation Tests</v>
+      </c>
+      <c r="B11" t="str">
+        <v>44/44 Passed</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Functional Tests</v>
+      </c>
+      <c r="B12" t="str">
+        <v>88/88 Passed</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F176"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="80.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Suite</v>
+      </c>
+      <c r="C1" t="str">
+        <v>TestName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E1" t="str">
+        <v>DurationMs</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Errors</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B2" t="str">
         <v>proposals.spec.ts</v>
       </c>
+      <c r="C2" t="str">
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
+      </c>
+      <c r="D2" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E2">
+        <v>2982</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B3" t="str">
+        <v>proposals.spec.ts</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
+      </c>
+      <c r="D3" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E3">
+        <v>2796</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B4" t="str">
+        <v>proposals.spec.ts</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
+      </c>
+      <c r="D4" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E4">
+        <v>2729</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B5" t="str">
+        <v>proposals.spec.ts</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
+      </c>
+      <c r="D5" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E5">
+        <v>2633</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Functional Test</v>
+      </c>
       <c r="B6" t="str">
+        <v>proposals.spec.ts</v>
+      </c>
+      <c r="C6" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
       </c>
-      <c r="C6" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D6">
-        <v>2944</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="D6" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E6">
+        <v>2873</v>
+      </c>
+      <c r="F6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B7" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
       </c>
-      <c r="C7" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D7">
-        <v>2638</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="D7" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E7">
+        <v>2705</v>
+      </c>
+      <c r="F7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B8" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
       </c>
-      <c r="C8" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D8">
-        <v>2666</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="D8" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E8">
+        <v>2650</v>
+      </c>
+      <c r="F8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B9" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
       </c>
-      <c r="C9" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D9">
-        <v>2570</v>
-      </c>
-      <c r="E9" t="str">
+      <c r="D9" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E9">
+        <v>2818</v>
+      </c>
+      <c r="F9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B10" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B10" t="str">
+      <c r="C10" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
       </c>
-      <c r="C10" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D10">
-        <v>2444</v>
-      </c>
-      <c r="E10" t="str">
+      <c r="D10" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E10">
+        <v>2638</v>
+      </c>
+      <c r="F10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B11" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B11" t="str">
+      <c r="C11" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
       </c>
-      <c r="C11" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D11">
-        <v>2693</v>
-      </c>
-      <c r="E11" t="str">
+      <c r="D11" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E11">
+        <v>2602</v>
+      </c>
+      <c r="F11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B12" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B12" t="str">
+      <c r="C12" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
       </c>
-      <c r="C12" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D12">
-        <v>2834</v>
-      </c>
-      <c r="E12" t="str">
+      <c r="D12" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E12">
+        <v>2645</v>
+      </c>
+      <c r="F12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B13" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
       </c>
-      <c r="C13" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D13">
-        <v>2679</v>
-      </c>
-      <c r="E13" t="str">
+      <c r="D13" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E13">
+        <v>2621</v>
+      </c>
+      <c r="F13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B14" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
       </c>
-      <c r="C14" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D14">
-        <v>2650</v>
-      </c>
-      <c r="E14" t="str">
+      <c r="D14" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E14">
+        <v>2726</v>
+      </c>
+      <c r="F14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B15" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B15" t="str">
+      <c r="C15" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
       </c>
-      <c r="C15" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D15">
-        <v>2711</v>
-      </c>
-      <c r="E15" t="str">
+      <c r="D15" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E15">
+        <v>2487</v>
+      </c>
+      <c r="F15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B16" t="str">
         <v>proposals.spec.ts</v>
       </c>
-      <c r="B16" t="str">
+      <c r="C16" t="str">
         <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
       </c>
-      <c r="C16" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D16">
-        <v>2605</v>
-      </c>
-      <c r="E16" t="str">
+      <c r="D16" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E16">
+        <v>2616</v>
+      </c>
+      <c r="F16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B17" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B17" t="str">
+      <c r="C17" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
       </c>
-      <c r="C17" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D17">
-        <v>1370</v>
-      </c>
-      <c r="E17" t="str">
+      <c r="D17" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E17">
+        <v>1415</v>
+      </c>
+      <c r="F17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B18" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B18" t="str">
+      <c r="C18" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
       </c>
-      <c r="C18" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D18">
-        <v>1542</v>
-      </c>
-      <c r="E18" t="str">
+      <c r="D18" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E18">
+        <v>1394</v>
+      </c>
+      <c r="F18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B19" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B19" t="str">
+      <c r="C19" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
       </c>
-      <c r="C19" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D19">
-        <v>1600</v>
-      </c>
-      <c r="E19" t="str">
+      <c r="D19" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E19">
+        <v>1707</v>
+      </c>
+      <c r="F19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B20" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B20" t="str">
+      <c r="C20" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
       </c>
-      <c r="C20" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D20">
-        <v>1807</v>
-      </c>
-      <c r="E20" t="str">
+      <c r="D20" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E20">
+        <v>1391</v>
+      </c>
+      <c r="F20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B21" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B21" t="str">
+      <c r="C21" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
       </c>
-      <c r="C21" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D21">
-        <v>1719</v>
-      </c>
-      <c r="E21" t="str">
+      <c r="D21" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E21">
+        <v>1581</v>
+      </c>
+      <c r="F21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B22" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B22" t="str">
+      <c r="C22" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
       </c>
-      <c r="C22" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D22">
-        <v>1712</v>
-      </c>
-      <c r="E22" t="str">
+      <c r="D22" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E22">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B23" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B23" t="str">
+      <c r="C23" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
       </c>
-      <c r="C23" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D23">
-        <v>1741</v>
-      </c>
-      <c r="E23" t="str">
+      <c r="D23" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E23">
+        <v>1483</v>
+      </c>
+      <c r="F23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B24" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B24" t="str">
+      <c r="C24" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
       </c>
-      <c r="C24" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D24">
-        <v>1758</v>
-      </c>
-      <c r="E24" t="str">
+      <c r="D24" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E24">
+        <v>1550</v>
+      </c>
+      <c r="F24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B25" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B25" t="str">
+      <c r="C25" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
       </c>
-      <c r="C25" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D25">
-        <v>1710</v>
-      </c>
-      <c r="E25" t="str">
+      <c r="D25" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E25">
+        <v>1649</v>
+      </c>
+      <c r="F25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B26" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B26" t="str">
+      <c r="C26" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
       </c>
-      <c r="C26" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D26">
-        <v>1665</v>
-      </c>
-      <c r="E26" t="str">
+      <c r="D26" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E26">
+        <v>1583</v>
+      </c>
+      <c r="F26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B27" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B27" t="str">
+      <c r="C27" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
       </c>
-      <c r="C27" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D27">
-        <v>1745</v>
-      </c>
-      <c r="E27" t="str">
+      <c r="D27" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E27">
+        <v>1430</v>
+      </c>
+      <c r="F27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B28" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B28" t="str">
+      <c r="C28" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
       </c>
-      <c r="C28" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D28">
-        <v>1516</v>
-      </c>
-      <c r="E28" t="str">
+      <c r="D28" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E28">
+        <v>1422</v>
+      </c>
+      <c r="F28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B29" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B29" t="str">
+      <c r="C29" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
       </c>
-      <c r="C29" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D29">
-        <v>1751</v>
-      </c>
-      <c r="E29" t="str">
+      <c r="D29" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E29">
+        <v>1640</v>
+      </c>
+      <c r="F29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B30" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B30" t="str">
+      <c r="C30" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
       </c>
-      <c r="C30" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D30">
-        <v>1759</v>
-      </c>
-      <c r="E30" t="str">
+      <c r="D30" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E30">
+        <v>1641</v>
+      </c>
+      <c r="F30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B31" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B31" t="str">
+      <c r="C31" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
       </c>
-      <c r="C31" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D31">
-        <v>1749</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="D31" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E31">
+        <v>1476</v>
+      </c>
+      <c r="F31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B32" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B32" t="str">
+      <c r="C32" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
       </c>
-      <c r="C32" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D32">
-        <v>1726</v>
-      </c>
-      <c r="E32" t="str">
+      <c r="D32" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E32">
+        <v>1565</v>
+      </c>
+      <c r="F32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B33" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B33" t="str">
+      <c r="C33" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
       </c>
-      <c r="C33" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D33">
-        <v>1546</v>
-      </c>
-      <c r="E33" t="str">
+      <c r="D33" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E33">
+        <v>1661</v>
+      </c>
+      <c r="F33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B34" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B34" t="str">
+      <c r="C34" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
       </c>
-      <c r="C34" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D34">
-        <v>1752</v>
-      </c>
-      <c r="E34" t="str">
+      <c r="D34" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E34">
+        <v>1588</v>
+      </c>
+      <c r="F34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B35" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B35" t="str">
+      <c r="C35" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
       </c>
-      <c r="C35" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D35">
-        <v>1695</v>
-      </c>
-      <c r="E35" t="str">
+      <c r="D35" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E35">
+        <v>1636</v>
+      </c>
+      <c r="F35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B36" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B36" t="str">
+      <c r="C36" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
       </c>
-      <c r="C36" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D36">
-        <v>1520</v>
-      </c>
-      <c r="E36" t="str">
+      <c r="D36" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E36">
+        <v>1402</v>
+      </c>
+      <c r="F36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B37" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B37" t="str">
+      <c r="C37" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
       </c>
-      <c r="C37" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D37">
-        <v>1665</v>
-      </c>
-      <c r="E37" t="str">
+      <c r="D37" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E37">
+        <v>1619</v>
+      </c>
+      <c r="F37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B38" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B38" t="str">
+      <c r="C38" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
       </c>
-      <c r="C38" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D38">
-        <v>1644</v>
-      </c>
-      <c r="E38" t="str">
+      <c r="D38" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E38">
+        <v>1363</v>
+      </c>
+      <c r="F38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B39" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B39" t="str">
+      <c r="C39" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
       </c>
-      <c r="C39" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D39">
-        <v>1469</v>
-      </c>
-      <c r="E39" t="str">
+      <c r="D39" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E39">
+        <v>1381</v>
+      </c>
+      <c r="F39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B40" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B40" t="str">
+      <c r="C40" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
       </c>
-      <c r="C40" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D40">
-        <v>1764</v>
-      </c>
-      <c r="E40" t="str">
+      <c r="D40" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E40">
+        <v>1454</v>
+      </c>
+      <c r="F40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B41" t="str">
         <v>project-creation.spec.ts</v>
       </c>
-      <c r="B41" t="str">
+      <c r="C41" t="str">
         <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
       </c>
-      <c r="C41" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D41">
-        <v>1658</v>
-      </c>
-      <c r="E41" t="str">
+      <c r="D41" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E41">
+        <v>1585</v>
+      </c>
+      <c r="F41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>uiux.spec.ts</v>
+        <v>Functional Test</v>
       </c>
       <c r="B42" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 1] Render Landing Page cleanly at Mobile Portrait (375x667)</v>
+        <v>proposal-workflow.spec.ts</v>
       </c>
       <c r="C42" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D42">
-        <v>2156</v>
-      </c>
-      <c r="E42" t="str">
+        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
+      </c>
+      <c r="D42" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E42">
+        <v>13628</v>
+      </c>
+      <c r="F42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B43" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B43" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 2] Render Landing Page cleanly at Mobile Landscape (667x375)</v>
-      </c>
       <c r="C43" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D43">
-        <v>1020</v>
-      </c>
-      <c r="E43" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 1] Render Landing Page cleanly at Mobile Portrait (375x667)</v>
+      </c>
+      <c r="D43" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E43">
+        <v>2075</v>
+      </c>
+      <c r="F43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B44" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B44" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 3] Render Landing Page cleanly at Tablet Portrait (768x1024)</v>
-      </c>
       <c r="C44" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D44">
-        <v>968</v>
-      </c>
-      <c r="E44" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 2] Render Landing Page cleanly at Mobile Landscape (667x375)</v>
+      </c>
+      <c r="D44" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E44">
+        <v>1038</v>
+      </c>
+      <c r="F44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B45" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B45" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 4] Render Landing Page cleanly at Tablet Landscape (1024x768)</v>
-      </c>
       <c r="C45" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D45">
-        <v>934</v>
-      </c>
-      <c r="E45" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 3] Render Landing Page cleanly at Tablet Portrait (768x1024)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E45">
+        <v>957</v>
+      </c>
+      <c r="F45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B46" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B46" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 5] Render Landing Page cleanly at Desktop Small (1280x800)</v>
-      </c>
       <c r="C46" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D46">
-        <v>943</v>
-      </c>
-      <c r="E46" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 4] Render Landing Page cleanly at Tablet Landscape (1024x768)</v>
+      </c>
+      <c r="D46" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E46">
+        <v>944</v>
+      </c>
+      <c r="F46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B47" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B47" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 6] Render Landing Page cleanly at Desktop Large (1920x1080)</v>
-      </c>
       <c r="C47" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D47">
-        <v>948</v>
-      </c>
-      <c r="E47" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 5] Render Landing Page cleanly at Desktop Small (1280x800)</v>
+      </c>
+      <c r="D47" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E47">
+        <v>963</v>
+      </c>
+      <c r="F47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B48" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B48" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 7] Render Login Page cleanly at Mobile Portrait (375x667)</v>
-      </c>
       <c r="C48" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D48">
-        <v>954</v>
-      </c>
-      <c r="E48" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 6] Render Landing Page cleanly at Desktop Large (1920x1080)</v>
+      </c>
+      <c r="D48" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E48">
+        <v>935</v>
+      </c>
+      <c r="F48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B49" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B49" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 8] Render Login Page cleanly at Mobile Landscape (667x375)</v>
-      </c>
       <c r="C49" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D49">
-        <v>974</v>
-      </c>
-      <c r="E49" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 7] Render Login Page cleanly at Mobile Portrait (375x667)</v>
+      </c>
+      <c r="D49" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E49">
+        <v>1013</v>
+      </c>
+      <c r="F49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B50" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B50" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 9] Render Login Page cleanly at Tablet Portrait (768x1024)</v>
-      </c>
       <c r="C50" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D50">
-        <v>973</v>
-      </c>
-      <c r="E50" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 8] Render Login Page cleanly at Mobile Landscape (667x375)</v>
+      </c>
+      <c r="D50" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E50">
+        <v>964</v>
+      </c>
+      <c r="F50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B51" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B51" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 10] Render Login Page cleanly at Tablet Landscape (1024x768)</v>
-      </c>
       <c r="C51" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D51">
-        <v>961</v>
-      </c>
-      <c r="E51" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 9] Render Login Page cleanly at Tablet Portrait (768x1024)</v>
+      </c>
+      <c r="D51" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E51">
+        <v>955</v>
+      </c>
+      <c r="F51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B52" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B52" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 11] Render Login Page cleanly at Desktop Small (1280x800)</v>
-      </c>
       <c r="C52" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D52">
-        <v>977</v>
-      </c>
-      <c r="E52" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 10] Render Login Page cleanly at Tablet Landscape (1024x768)</v>
+      </c>
+      <c r="D52" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E52">
+        <v>957</v>
+      </c>
+      <c r="F52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B53" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B53" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 12] Render Login Page cleanly at Desktop Large (1920x1080)</v>
-      </c>
       <c r="C53" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D53">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 11] Render Login Page cleanly at Desktop Small (1280x800)</v>
+      </c>
+      <c r="D53" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E53">
         <v>950</v>
       </c>
-      <c r="E53" t="str">
+      <c r="F53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B54" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B54" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 13] Render Register Page cleanly at Mobile Portrait (375x667)</v>
-      </c>
       <c r="C54" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D54">
-        <v>979</v>
-      </c>
-      <c r="E54" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 12] Render Login Page cleanly at Desktop Large (1920x1080)</v>
+      </c>
+      <c r="D54" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E54">
+        <v>965</v>
+      </c>
+      <c r="F54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B55" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B55" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 14] Render Register Page cleanly at Mobile Landscape (667x375)</v>
-      </c>
       <c r="C55" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D55">
-        <v>950</v>
-      </c>
-      <c r="E55" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 13] Render Register Page cleanly at Mobile Portrait (375x667)</v>
+      </c>
+      <c r="D55" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E55">
+        <v>962</v>
+      </c>
+      <c r="F55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B56" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B56" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 15] Render Register Page cleanly at Tablet Portrait (768x1024)</v>
-      </c>
       <c r="C56" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D56">
-        <v>967</v>
-      </c>
-      <c r="E56" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 14] Render Register Page cleanly at Mobile Landscape (667x375)</v>
+      </c>
+      <c r="D56" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E56">
+        <v>962</v>
+      </c>
+      <c r="F56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B57" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B57" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 16] Render Register Page cleanly at Tablet Landscape (1024x768)</v>
-      </c>
       <c r="C57" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D57">
-        <v>954</v>
-      </c>
-      <c r="E57" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 15] Render Register Page cleanly at Tablet Portrait (768x1024)</v>
+      </c>
+      <c r="D57" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E57">
+        <v>1004</v>
+      </c>
+      <c r="F57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B58" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B58" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 17] Render Register Page cleanly at Desktop Small (1280x800)</v>
-      </c>
       <c r="C58" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D58">
-        <v>974</v>
-      </c>
-      <c r="E58" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 16] Render Register Page cleanly at Tablet Landscape (1024x768)</v>
+      </c>
+      <c r="D58" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E58">
+        <v>948</v>
+      </c>
+      <c r="F58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B59" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B59" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 18] Render Register Page cleanly at Desktop Large (1920x1080)</v>
-      </c>
       <c r="C59" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D59">
-        <v>957</v>
-      </c>
-      <c r="E59" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 17] Render Register Page cleanly at Desktop Small (1280x800)</v>
+      </c>
+      <c r="D59" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E59">
+        <v>968</v>
+      </c>
+      <c r="F59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B60" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B60" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 19] Render Dashboard cleanly at Mobile Portrait (375x667)</v>
-      </c>
       <c r="C60" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D60">
-        <v>987</v>
-      </c>
-      <c r="E60" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 18] Render Register Page cleanly at Desktop Large (1920x1080)</v>
+      </c>
+      <c r="D60" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E60">
+        <v>957</v>
+      </c>
+      <c r="F60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B61" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B61" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 20] Render Dashboard cleanly at Mobile Landscape (667x375)</v>
-      </c>
       <c r="C61" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D61">
-        <v>956</v>
-      </c>
-      <c r="E61" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 19] Render Dashboard cleanly at Mobile Portrait (375x667)</v>
+      </c>
+      <c r="D61" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E61">
+        <v>1013</v>
+      </c>
+      <c r="F61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B62" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B62" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 21] Render Dashboard cleanly at Tablet Portrait (768x1024)</v>
-      </c>
       <c r="C62" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D62">
-        <v>958</v>
-      </c>
-      <c r="E62" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 20] Render Dashboard cleanly at Mobile Landscape (667x375)</v>
+      </c>
+      <c r="D62" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E62">
+        <v>984</v>
+      </c>
+      <c r="F62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B63" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B63" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 22] Render Dashboard cleanly at Tablet Landscape (1024x768)</v>
-      </c>
       <c r="C63" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D63">
-        <v>959</v>
-      </c>
-      <c r="E63" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 21] Render Dashboard cleanly at Tablet Portrait (768x1024)</v>
+      </c>
+      <c r="D63" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E63">
+        <v>978</v>
+      </c>
+      <c r="F63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B64" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B64" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 23] Render Dashboard cleanly at Desktop Small (1280x800)</v>
-      </c>
       <c r="C64" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D64">
-        <v>1033</v>
-      </c>
-      <c r="E64" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 22] Render Dashboard cleanly at Tablet Landscape (1024x768)</v>
+      </c>
+      <c r="D64" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E64">
+        <v>954</v>
+      </c>
+      <c r="F64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B65" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B65" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) [Case 24] Render Dashboard cleanly at Desktop Large (1920x1080)</v>
-      </c>
       <c r="C65" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D65">
-        <v>967</v>
-      </c>
-      <c r="E65" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 23] Render Dashboard cleanly at Desktop Small (1280x800)</v>
+      </c>
+      <c r="D65" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E65">
+        <v>957</v>
+      </c>
+      <c r="F65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
+        <v>UI/UX Test</v>
+      </c>
+      <c r="B66" t="str">
         <v>uiux.spec.ts</v>
       </c>
-      <c r="B66" t="str">
-        <v>UI/UX Responsive Testing (15+ Cases) Toggles dark/light mode successfully</v>
-      </c>
       <c r="C66" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D66">
-        <v>1468</v>
-      </c>
-      <c r="E66" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) [Case 24] Render Dashboard cleanly at Desktop Large (1920x1080)</v>
+      </c>
+      <c r="D66" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E66">
+        <v>946</v>
+      </c>
+      <c r="F66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>auth-validation.spec.ts</v>
+        <v>UI/UX Test</v>
       </c>
       <c r="B67" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - empty name should prevent registration with empty name</v>
+        <v>uiux.spec.ts</v>
       </c>
       <c r="C67" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D67">
-        <v>928</v>
-      </c>
-      <c r="E67" t="str">
+        <v>UI/UX Responsive Testing (15+ Cases) Toggles dark/light mode successfully</v>
+      </c>
+      <c r="D67" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E67">
+        <v>1455</v>
+      </c>
+      <c r="F67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B68" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B68" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - very short name should prevent registration with very short name</v>
-      </c>
       <c r="C68" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D68">
-        <v>629</v>
-      </c>
-      <c r="E68" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - empty name should prevent registration with empty name</v>
+      </c>
+      <c r="D68" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E68">
+        <v>1713</v>
+      </c>
+      <c r="F68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B69" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B69" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - invalid email format should prevent registration with invalid email format</v>
-      </c>
       <c r="C69" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D69">
-        <v>653</v>
-      </c>
-      <c r="E69" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - very short name should prevent registration with very short name</v>
+      </c>
+      <c r="D69" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E69">
+        <v>731</v>
+      </c>
+      <c r="F69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B70" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B70" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - empty email should prevent registration with empty email</v>
-      </c>
       <c r="C70" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D70">
-        <v>535</v>
-      </c>
-      <c r="E70" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - invalid email format should prevent registration with invalid email format</v>
+      </c>
+      <c r="D70" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E70">
+        <v>787</v>
+      </c>
+      <c r="F70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B71" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B71" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - incomplete email should prevent registration with incomplete email</v>
-      </c>
       <c r="C71" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D71">
-        <v>639</v>
-      </c>
-      <c r="E71" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - empty email should prevent registration with empty email</v>
+      </c>
+      <c r="D71" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E71">
+        <v>586</v>
+      </c>
+      <c r="F71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B72" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B72" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - empty password should prevent registration with empty password</v>
-      </c>
       <c r="C72" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D72">
-        <v>575</v>
-      </c>
-      <c r="E72" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - incomplete email should prevent registration with incomplete email</v>
+      </c>
+      <c r="D72" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E72">
+        <v>942</v>
+      </c>
+      <c r="F72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B73" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B73" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - password too short should prevent registration with password too short</v>
-      </c>
       <c r="C73" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D73">
-        <v>594</v>
-      </c>
-      <c r="E73" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - empty password should prevent registration with empty password</v>
+      </c>
+      <c r="D73" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E73">
+        <v>801</v>
+      </c>
+      <c r="F73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B74" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B74" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - password no uppercase should prevent registration with password no uppercase</v>
-      </c>
       <c r="C74" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D74">
-        <v>665</v>
-      </c>
-      <c r="E74" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - password too short should prevent registration with password too short</v>
+      </c>
+      <c r="D74" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E74">
+        <v>767</v>
+      </c>
+      <c r="F74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B75" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B75" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - password no lowercase should prevent registration with password no lowercase</v>
-      </c>
       <c r="C75" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D75">
-        <v>682</v>
-      </c>
-      <c r="E75" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - password no uppercase should prevent registration with password no uppercase</v>
+      </c>
+      <c r="D75" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E75">
+        <v>1131</v>
+      </c>
+      <c r="F75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B76" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B76" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - password no numbers should prevent registration with password no numbers</v>
-      </c>
       <c r="C76" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D76">
-        <v>851</v>
-      </c>
-      <c r="E76" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - password no lowercase should prevent registration with password no lowercase</v>
+      </c>
+      <c r="D76" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E76">
+        <v>1049</v>
+      </c>
+      <c r="F76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B77" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B77" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - passwords do not match should prevent registration with passwords do not match</v>
-      </c>
       <c r="C77" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D77">
-        <v>629</v>
-      </c>
-      <c r="E77" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - password no numbers should prevent registration with password no numbers</v>
+      </c>
+      <c r="D77" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E77">
+        <v>945</v>
+      </c>
+      <c r="F77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B78" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B78" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: client - existing email should prevent registration with existing email</v>
-      </c>
       <c r="C78" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D78">
-        <v>834</v>
-      </c>
-      <c r="E78" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - passwords do not match should prevent registration with passwords do not match</v>
+      </c>
+      <c r="D78" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E78">
+        <v>987</v>
+      </c>
+      <c r="F78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B79" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B79" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty name should prevent registration with empty name</v>
-      </c>
       <c r="C79" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D79">
-        <v>521</v>
-      </c>
-      <c r="E79" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: client - existing email should prevent registration with existing email</v>
+      </c>
+      <c r="D79" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E79">
+        <v>957</v>
+      </c>
+      <c r="F79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B80" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B80" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - very short name should prevent registration with very short name</v>
-      </c>
       <c r="C80" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D80">
-        <v>691</v>
-      </c>
-      <c r="E80" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty name should prevent registration with empty name</v>
+      </c>
+      <c r="D80" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E80">
+        <v>784</v>
+      </c>
+      <c r="F80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B81" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B81" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - invalid email format should prevent registration with invalid email format</v>
-      </c>
       <c r="C81" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D81">
-        <v>650</v>
-      </c>
-      <c r="E81" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - very short name should prevent registration with very short name</v>
+      </c>
+      <c r="D81" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E81">
+        <v>807</v>
+      </c>
+      <c r="F81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B82" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B82" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty email should prevent registration with empty email</v>
-      </c>
       <c r="C82" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D82">
-        <v>528</v>
-      </c>
-      <c r="E82" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - invalid email format should prevent registration with invalid email format</v>
+      </c>
+      <c r="D82" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E82">
+        <v>841</v>
+      </c>
+      <c r="F82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B83" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B83" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - incomplete email should prevent registration with incomplete email</v>
-      </c>
       <c r="C83" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D83">
-        <v>618</v>
-      </c>
-      <c r="E83" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty email should prevent registration with empty email</v>
+      </c>
+      <c r="D83" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E83">
+        <v>935</v>
+      </c>
+      <c r="F83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B84" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B84" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty password should prevent registration with empty password</v>
-      </c>
       <c r="C84" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D84">
-        <v>495</v>
-      </c>
-      <c r="E84" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - incomplete email should prevent registration with incomplete email</v>
+      </c>
+      <c r="D84" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E84">
+        <v>1055</v>
+      </c>
+      <c r="F84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B85" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B85" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password too short should prevent registration with password too short</v>
-      </c>
       <c r="C85" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D85">
-        <v>534</v>
-      </c>
-      <c r="E85" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - empty password should prevent registration with empty password</v>
+      </c>
+      <c r="D85" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E85">
+        <v>774</v>
+      </c>
+      <c r="F85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B86" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B86" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no uppercase should prevent registration with password no uppercase</v>
-      </c>
       <c r="C86" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D86">
-        <v>631</v>
-      </c>
-      <c r="E86" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password too short should prevent registration with password too short</v>
+      </c>
+      <c r="D86" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E86">
+        <v>845</v>
+      </c>
+      <c r="F86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B87" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B87" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no lowercase should prevent registration with password no lowercase</v>
-      </c>
       <c r="C87" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D87">
-        <v>777</v>
-      </c>
-      <c r="E87" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no uppercase should prevent registration with password no uppercase</v>
+      </c>
+      <c r="D87" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E87">
+        <v>986</v>
+      </c>
+      <c r="F87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B88" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B88" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no numbers should prevent registration with password no numbers</v>
-      </c>
       <c r="C88" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D88">
-        <v>632</v>
-      </c>
-      <c r="E88" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no lowercase should prevent registration with password no lowercase</v>
+      </c>
+      <c r="D88" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E88">
+        <v>940</v>
+      </c>
+      <c r="F88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B89" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B89" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - passwords do not match should prevent registration with passwords do not match</v>
-      </c>
       <c r="C89" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D89">
-        <v>613</v>
-      </c>
-      <c r="E89" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - password no numbers should prevent registration with password no numbers</v>
+      </c>
+      <c r="D89" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E89">
+        <v>945</v>
+      </c>
+      <c r="F89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B90" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B90" t="str">
-        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - existing email should prevent registration with existing email</v>
-      </c>
       <c r="C90" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D90">
-        <v>608</v>
-      </c>
-      <c r="E90" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - passwords do not match should prevent registration with passwords do not match</v>
+      </c>
+      <c r="D90" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E90">
+        <v>1043</v>
+      </c>
+      <c r="F90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B91" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B91" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: empty email should prevent login with empty email</v>
-      </c>
       <c r="C91" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D91">
-        <v>285</v>
-      </c>
-      <c r="E91" t="str">
+        <v>Auth Validation (30+ Cases) Registration Validation: freelancer - existing email should prevent registration with existing email</v>
+      </c>
+      <c r="D91" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E91">
+        <v>1093</v>
+      </c>
+      <c r="F91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B92" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B92" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: invalid email should prevent login with invalid email</v>
-      </c>
       <c r="C92" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D92">
-        <v>375</v>
-      </c>
-      <c r="E92" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: empty email should prevent login with empty email</v>
+      </c>
+      <c r="D92" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E92">
+        <v>510</v>
+      </c>
+      <c r="F92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B93" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B93" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: empty password should prevent login with empty password</v>
-      </c>
       <c r="C93" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D93">
-        <v>366</v>
-      </c>
-      <c r="E93" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: invalid email should prevent login with invalid email</v>
+      </c>
+      <c r="D93" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E93">
+        <v>693</v>
+      </c>
+      <c r="F93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B94" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B94" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: wrong password should prevent login with wrong password</v>
-      </c>
       <c r="C94" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D94">
-        <v>510</v>
-      </c>
-      <c r="E94" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: empty password should prevent login with empty password</v>
+      </c>
+      <c r="D94" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E94">
+        <v>443</v>
+      </c>
+      <c r="F94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B95" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B95" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: unregistered email should prevent login with unregistered email</v>
-      </c>
       <c r="C95" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D95">
-        <v>565</v>
-      </c>
-      <c r="E95" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: wrong password should prevent login with wrong password</v>
+      </c>
+      <c r="D95" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E95">
+        <v>673</v>
+      </c>
+      <c r="F95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B96" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B96" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: SQL injection string in email should prevent login with SQL injection string in email</v>
-      </c>
       <c r="C96" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D96">
-        <v>482</v>
-      </c>
-      <c r="E96" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: unregistered email should prevent login with unregistered email</v>
+      </c>
+      <c r="D96" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E96">
+        <v>689</v>
+      </c>
+      <c r="F96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B97" t="str">
         <v>auth-validation.spec.ts</v>
       </c>
-      <c r="B97" t="str">
-        <v>Auth Validation (30+ Cases) Login Validation: XSS string in email should prevent login with XSS string in email</v>
-      </c>
       <c r="C97" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D97">
-        <v>552</v>
-      </c>
-      <c r="E97" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: SQL injection string in email should prevent login with SQL injection string in email</v>
+      </c>
+      <c r="D97" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E97">
+        <v>679</v>
+      </c>
+      <c r="F97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>search.spec.ts</v>
+        <v>Validation Test</v>
       </c>
       <c r="B98" t="str">
-        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
+        <v>auth-validation.spec.ts</v>
       </c>
       <c r="C98" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D98">
-        <v>762</v>
-      </c>
-      <c r="E98" t="str">
+        <v>Auth Validation (30+ Cases) Login Validation: XSS string in email should prevent login with XSS string in email</v>
+      </c>
+      <c r="D98" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E98">
+        <v>803</v>
+      </c>
+      <c r="F98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B99" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B99" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
-      </c>
       <c r="C99" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D99">
-        <v>720</v>
-      </c>
-      <c r="E99" t="str">
+        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
+      </c>
+      <c r="D99" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E99">
+        <v>787</v>
+      </c>
+      <c r="F99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B100" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B100" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
-      </c>
       <c r="C100" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D100">
-        <v>764</v>
-      </c>
-      <c r="E100" t="str">
+        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
+      </c>
+      <c r="D100" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E100">
+        <v>739</v>
+      </c>
+      <c r="F100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B101" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B101" t="str">
-        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
-      </c>
       <c r="C101" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D101">
-        <v>761</v>
-      </c>
-      <c r="E101" t="str">
+        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
+      </c>
+      <c r="D101" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E101">
+        <v>773</v>
+      </c>
+      <c r="F101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B102" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B102" t="str">
-        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
-      </c>
       <c r="C102" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D102">
-        <v>744</v>
-      </c>
-      <c r="E102" t="str">
+        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
+      </c>
+      <c r="D102" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E102">
+        <v>766</v>
+      </c>
+      <c r="F102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B103" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B103" t="str">
-        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
-      </c>
       <c r="C103" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D103">
-        <v>780</v>
-      </c>
-      <c r="E103" t="str">
+        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
+      </c>
+      <c r="D103" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E103">
+        <v>742</v>
+      </c>
+      <c r="F103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B104" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B104" t="str">
-        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
-      </c>
       <c r="C104" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D104">
-        <v>777</v>
-      </c>
-      <c r="E104" t="str">
+        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
+      </c>
+      <c r="D104" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E104">
+        <v>800</v>
+      </c>
+      <c r="F104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B105" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B105" t="str">
-        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
-      </c>
       <c r="C105" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D105">
-        <v>780</v>
-      </c>
-      <c r="E105" t="str">
+        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
+      </c>
+      <c r="D105" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E105">
+        <v>860</v>
+      </c>
+      <c r="F105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B106" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B106" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
-      </c>
       <c r="C106" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D106">
-        <v>740</v>
-      </c>
-      <c r="E106" t="str">
+        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
+      </c>
+      <c r="D106" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E106">
+        <v>1021</v>
+      </c>
+      <c r="F106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B107" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B107" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
-      </c>
       <c r="C107" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D107">
-        <v>743</v>
-      </c>
-      <c r="E107" t="str">
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
+      </c>
+      <c r="D107" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E107">
+        <v>852</v>
+      </c>
+      <c r="F107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B108" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B108" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
-      </c>
       <c r="C108" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D108">
-        <v>782</v>
-      </c>
-      <c r="E108" t="str">
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
+      </c>
+      <c r="D108" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E108">
+        <v>786</v>
+      </c>
+      <c r="F108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B109" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B109" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
-      </c>
       <c r="C109" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D109">
-        <v>722</v>
-      </c>
-      <c r="E109" t="str">
+        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
+      </c>
+      <c r="D109" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E109">
+        <v>789</v>
+      </c>
+      <c r="F109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B110" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B110" t="str">
-        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
-      </c>
       <c r="C110" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D110">
-        <v>1027</v>
-      </c>
-      <c r="E110" t="str">
+        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
+      </c>
+      <c r="D110" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E110">
+        <v>810</v>
+      </c>
+      <c r="F110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B111" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B111" t="str">
-        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
-      </c>
       <c r="C111" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D111">
-        <v>767</v>
-      </c>
-      <c r="E111" t="str">
+        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
+      </c>
+      <c r="D111" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E111">
+        <v>1499</v>
+      </c>
+      <c r="F111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B112" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B112" t="str">
-        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
-      </c>
       <c r="C112" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D112">
-        <v>789</v>
-      </c>
-      <c r="E112" t="str">
+        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
+      </c>
+      <c r="D112" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E112">
+        <v>980</v>
+      </c>
+      <c r="F112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B113" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B113" t="str">
-        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
-      </c>
       <c r="C113" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D113">
-        <v>788</v>
-      </c>
-      <c r="E113" t="str">
+        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
+      </c>
+      <c r="D113" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E113">
+        <v>986</v>
+      </c>
+      <c r="F113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B114" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B114" t="str">
-        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
-      </c>
       <c r="C114" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D114">
-        <v>774</v>
-      </c>
-      <c r="E114" t="str">
+        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
+      </c>
+      <c r="D114" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E114">
+        <v>792</v>
+      </c>
+      <c r="F114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B115" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B115" t="str">
-        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
-      </c>
       <c r="C115" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D115">
-        <v>818</v>
-      </c>
-      <c r="E115" t="str">
+        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
+      </c>
+      <c r="D115" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E115">
+        <v>820</v>
+      </c>
+      <c r="F115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B116" t="str">
         <v>search.spec.ts</v>
       </c>
-      <c r="B116" t="str">
-        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
-      </c>
       <c r="C116" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D116">
-        <v>762</v>
-      </c>
-      <c r="E116" t="str">
+        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
+      </c>
+      <c r="D116" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E116">
+        <v>792</v>
+      </c>
+      <c r="F116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>validation.spec.ts</v>
+        <v>Functional Test</v>
       </c>
       <c r="B117" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 1] Login fails with: empty email / empty password</v>
+        <v>search.spec.ts</v>
       </c>
       <c r="C117" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D117">
-        <v>1140</v>
-      </c>
-      <c r="E117" t="str">
+        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
+      </c>
+      <c r="D117" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E117">
+        <v>804</v>
+      </c>
+      <c r="F117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B118" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B118" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 2] Login fails with: invalid / password123</v>
-      </c>
       <c r="C118" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D118">
-        <v>943</v>
-      </c>
-      <c r="E118" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 1] Login fails with: empty email / empty password</v>
+      </c>
+      <c r="D118" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E118">
+        <v>1181</v>
+      </c>
+      <c r="F118" t="str">
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B119" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B119" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 3] Login fails with: nonexistent@example.com / wrong</v>
-      </c>
       <c r="C119" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D119">
-        <v>937</v>
-      </c>
-      <c r="E119" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 2] Login fails with: invalid / password123</v>
+      </c>
+      <c r="D119" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E119">
+        <v>926</v>
+      </c>
+      <c r="F119" t="str">
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B120" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B120" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 4] Registration validation: Name required</v>
-      </c>
       <c r="C120" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D120">
-        <v>1066</v>
-      </c>
-      <c r="E120" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 3] Login fails with: nonexistent@example.com / wrong</v>
+      </c>
+      <c r="D120" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E120">
+        <v>913</v>
+      </c>
+      <c r="F120" t="str">
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B121" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B121" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 5] Registration validation: Invalid characters</v>
-      </c>
       <c r="C121" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D121">
-        <v>1240</v>
-      </c>
-      <c r="E121" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 4] Registration validation: Name required</v>
+      </c>
+      <c r="D121" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E121">
+        <v>1071</v>
+      </c>
+      <c r="F121" t="str">
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B122" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B122" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 6] Registration validation: Password must be at least 8 characters</v>
-      </c>
       <c r="C122" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D122">
-        <v>1091</v>
-      </c>
-      <c r="E122" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 5] Registration validation: Invalid characters</v>
+      </c>
+      <c r="D122" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E122">
+        <v>1321</v>
+      </c>
+      <c r="F122" t="str">
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B123" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B123" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 7] Registration validation: Passwords do not match</v>
-      </c>
       <c r="C123" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D123">
-        <v>1111</v>
-      </c>
-      <c r="E123" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 6] Registration validation: Password must be at least 8 characters</v>
+      </c>
+      <c r="D123" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E123">
+        <v>1084</v>
+      </c>
+      <c r="F123" t="str">
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B124" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B124" t="str">
-        <v>Validation Testing (30+ Cases) Authentication Validations [Case 8] Registration validation: Must agree to terms</v>
-      </c>
       <c r="C124" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D124">
-        <v>1155</v>
-      </c>
-      <c r="E124" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 7] Registration validation: Passwords do not match</v>
+      </c>
+      <c r="D124" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E124">
+        <v>1138</v>
+      </c>
+      <c r="F124" t="str">
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B125" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B125" t="str">
-        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 9] Project posting fails: Title missing</v>
-      </c>
       <c r="C125" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D125">
-        <v>1192</v>
-      </c>
-      <c r="E125" t="str">
+        <v>Validation Testing (30+ Cases) Authentication Validations [Case 8] Registration validation: Must agree to terms</v>
+      </c>
+      <c r="D125" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E125">
+        <v>1116</v>
+      </c>
+      <c r="F125" t="str">
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B126" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B126" t="str">
-        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 10] Project posting fails: Desc too short</v>
-      </c>
       <c r="C126" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D126">
-        <v>1168</v>
-      </c>
-      <c r="E126" t="str">
+        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 9] Project posting fails: Title missing</v>
+      </c>
+      <c r="D126" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E126">
+        <v>1169</v>
+      </c>
+      <c r="F126" t="str">
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B127" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B127" t="str">
-        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 11] Project posting fails: Negative budget</v>
-      </c>
       <c r="C127" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D127">
-        <v>1177</v>
-      </c>
-      <c r="E127" t="str">
+        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 10] Project posting fails: Desc too short</v>
+      </c>
+      <c r="D127" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E127">
+        <v>1173</v>
+      </c>
+      <c r="F127" t="str">
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B128" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B128" t="str">
-        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 12] Project posting fails: Zero budget</v>
-      </c>
       <c r="C128" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D128">
-        <v>1174</v>
-      </c>
-      <c r="E128" t="str">
+        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 11] Project posting fails: Negative budget</v>
+      </c>
+      <c r="D128" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E128">
+        <v>1173</v>
+      </c>
+      <c r="F128" t="str">
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
+        <v>Validation Test</v>
+      </c>
+      <c r="B129" t="str">
         <v>validation.spec.ts</v>
       </c>
-      <c r="B129" t="str">
-        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 13] Project posting fails: Title too long</v>
-      </c>
       <c r="C129" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D129">
-        <v>1181</v>
-      </c>
-      <c r="E129" t="str">
+        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 12] Project posting fails: Zero budget</v>
+      </c>
+      <c r="D129" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E129">
+        <v>1165</v>
+      </c>
+      <c r="F129" t="str">
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>proposal-workflow.spec.ts</v>
+        <v>Validation Test</v>
       </c>
       <c r="B130" t="str">
-        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
+        <v>validation.spec.ts</v>
       </c>
       <c r="C130" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D130">
-        <v>27583</v>
-      </c>
-      <c r="E130" t="str">
+        <v>Validation Testing (30+ Cases) Project Posting Validations [Case 13] Project posting fails: Title too long</v>
+      </c>
+      <c r="D130" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E130">
+        <v>1179</v>
+      </c>
+      <c r="F130" t="str">
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B131" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B131" t="str">
+      <c r="C131" t="str">
         <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
       </c>
-      <c r="C131" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D131">
-        <v>1225</v>
-      </c>
-      <c r="E131" t="str">
+      <c r="D131" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E131">
+        <v>1223</v>
+      </c>
+      <c r="F131" t="str">
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B132" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B132" t="str">
+      <c r="C132" t="str">
         <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
       </c>
-      <c r="C132" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D132">
-        <v>1257</v>
-      </c>
-      <c r="E132" t="str">
+      <c r="D132" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E132">
+        <v>1281</v>
+      </c>
+      <c r="F132" t="str">
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B133" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B133" t="str">
+      <c r="C133" t="str">
         <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
       </c>
-      <c r="C133" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D133">
-        <v>1154</v>
-      </c>
-      <c r="E133" t="str">
+      <c r="D133" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E133">
+        <v>1141</v>
+      </c>
+      <c r="F133" t="str">
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B134" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B134" t="str">
+      <c r="C134" t="str">
         <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
       </c>
-      <c r="C134" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D134">
-        <v>1188</v>
-      </c>
-      <c r="E134" t="str">
+      <c r="D134" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E134">
+        <v>1220</v>
+      </c>
+      <c r="F134" t="str">
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B135" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B135" t="str">
+      <c r="C135" t="str">
         <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
       </c>
-      <c r="C135" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D135">
-        <v>1157</v>
-      </c>
-      <c r="E135" t="str">
+      <c r="D135" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E135">
+        <v>1252</v>
+      </c>
+      <c r="F135" t="str">
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B136" t="str">
         <v>global-smoke.spec.ts</v>
       </c>
-      <c r="B136" t="str">
+      <c r="C136" t="str">
         <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
       </c>
-      <c r="C136" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D136">
-        <v>1147</v>
-      </c>
-      <c r="E136" t="str">
+      <c r="D136" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E136">
+        <v>1172</v>
+      </c>
+      <c r="F136" t="str">
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B137" t="str">
         <v>projects.spec.ts</v>
       </c>
-      <c r="B137" t="str">
+      <c r="C137" t="str">
         <v>Projects &amp; Kanban should create, filter, and view project details</v>
       </c>
-      <c r="C137" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D137">
-        <v>6107</v>
-      </c>
-      <c r="E137" t="str">
+      <c r="D137" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E137">
+        <v>6173</v>
+      </c>
+      <c r="F137" t="str">
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B138" t="str">
         <v>wallet.spec.ts</v>
       </c>
-      <c r="B138" t="str">
+      <c r="C138" t="str">
         <v>Wallet should view wallet page</v>
       </c>
-      <c r="C138" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D138">
-        <v>1577</v>
-      </c>
-      <c r="E138" t="str">
+      <c r="D138" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E138">
+        <v>1485</v>
+      </c>
+      <c r="F138" t="str">
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B139" t="str">
         <v>wallet.spec.ts</v>
       </c>
-      <c r="B139" t="str">
+      <c r="C139" t="str">
         <v>Wallet should withdraw funds and show toast</v>
       </c>
-      <c r="C139" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D139">
-        <v>1221</v>
-      </c>
-      <c r="E139" t="str">
+      <c r="D139" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E139">
+        <v>1440</v>
+      </c>
+      <c r="F139" t="str">
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B140" t="str">
         <v>wallet.spec.ts</v>
       </c>
-      <c r="B140" t="str">
+      <c r="C140" t="str">
         <v>Wallet should export CSV</v>
       </c>
-      <c r="C140" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D140">
-        <v>2348</v>
-      </c>
-      <c r="E140" t="str">
+      <c r="D140" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E140">
+        <v>2827</v>
+      </c>
+      <c r="F140" t="str">
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B141" t="str">
         <v>auth.spec.ts</v>
       </c>
-      <c r="B141" t="str">
+      <c r="C141" t="str">
         <v>Authentication &amp; Onboarding should navigate onboarding and login</v>
       </c>
-      <c r="C141" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D141">
-        <v>4677</v>
-      </c>
-      <c r="E141" t="str">
+      <c r="D141" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E141">
+        <v>5028</v>
+      </c>
+      <c r="F141" t="str">
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B142" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B142" t="str">
+      <c r="C142" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: empty name should handle profile update for empty name</v>
       </c>
-      <c r="C142" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D142">
-        <v>228</v>
-      </c>
-      <c r="E142" t="str">
+      <c r="D142" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E142">
+        <v>270</v>
+      </c>
+      <c r="F142" t="str">
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B143" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B143" t="str">
+      <c r="C143" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: too short name should handle profile update for too short name</v>
       </c>
-      <c r="C143" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D143">
-        <v>184</v>
-      </c>
-      <c r="E143" t="str">
+      <c r="D143" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E143">
+        <v>206</v>
+      </c>
+      <c r="F143" t="str">
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B144" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B144" t="str">
+      <c r="C144" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: empty bio should handle profile update for empty bio</v>
       </c>
-      <c r="C144" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D144">
-        <v>167</v>
-      </c>
-      <c r="E144" t="str">
+      <c r="D144" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E144">
+        <v>239</v>
+      </c>
+      <c r="F144" t="str">
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B145" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B145" t="str">
+      <c r="C145" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: too short bio should handle profile update for too short bio</v>
       </c>
-      <c r="C145" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D145">
-        <v>177</v>
-      </c>
-      <c r="E145" t="str">
+      <c r="D145" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E145">
+        <v>195</v>
+      </c>
+      <c r="F145" t="str">
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B146" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B146" t="str">
+      <c r="C146" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: too long bio should handle profile update for too long bio</v>
       </c>
-      <c r="C146" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D146">
-        <v>174</v>
-      </c>
-      <c r="E146" t="str">
+      <c r="D146" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E146">
+        <v>189</v>
+      </c>
+      <c r="F146" t="str">
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B147" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B147" t="str">
+      <c r="C147" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS name should handle profile update for XSS name</v>
       </c>
-      <c r="C147" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D147">
-        <v>236</v>
-      </c>
-      <c r="E147" t="str">
+      <c r="D147" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E147">
+        <v>220</v>
+      </c>
+      <c r="F147" t="str">
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B148" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B148" t="str">
+      <c r="C148" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS bio should handle profile update for XSS bio</v>
       </c>
-      <c r="C148" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D148">
-        <v>172</v>
-      </c>
-      <c r="E148" t="str">
+      <c r="D148" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E148">
+        <v>243</v>
+      </c>
+      <c r="F148" t="str">
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B149" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B149" t="str">
+      <c r="C149" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: empty skill should handle profile update for empty skill</v>
       </c>
-      <c r="C149" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D149">
-        <v>179</v>
-      </c>
-      <c r="E149" t="str">
+      <c r="D149" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E149">
+        <v>221</v>
+      </c>
+      <c r="F149" t="str">
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B150" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B150" t="str">
+      <c r="C150" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace skill should handle profile update for whitespace skill</v>
       </c>
-      <c r="C150" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D150">
-        <v>182</v>
-      </c>
-      <c r="E150" t="str">
+      <c r="D150" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E150">
+        <v>238</v>
+      </c>
+      <c r="F150" t="str">
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B151" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B151" t="str">
+      <c r="C151" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS skill should handle profile update for XSS skill</v>
       </c>
-      <c r="C151" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D151">
-        <v>184</v>
-      </c>
-      <c r="E151" t="str">
+      <c r="D151" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E151">
+        <v>260</v>
+      </c>
+      <c r="F151" t="str">
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B152" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B152" t="str">
+      <c r="C152" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: numeric skill should handle profile update for numeric skill</v>
       </c>
-      <c r="C152" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D152">
-        <v>226</v>
-      </c>
-      <c r="E152" t="str">
+      <c r="D152" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E152">
+        <v>207</v>
+      </c>
+      <c r="F152" t="str">
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B153" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B153" t="str">
+      <c r="C153" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: special characters skill should handle profile update for special characters skill</v>
       </c>
-      <c r="C153" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D153">
-        <v>193</v>
-      </c>
-      <c r="E153" t="str">
+      <c r="D153" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E153">
+        <v>220</v>
+      </c>
+      <c r="F153" t="str">
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B154" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B154" t="str">
+      <c r="C154" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: extremely long skill should handle profile update for extremely long skill</v>
       </c>
-      <c r="C154" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D154">
-        <v>190</v>
-      </c>
-      <c r="E154" t="str">
+      <c r="D154" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E154">
+        <v>210</v>
+      </c>
+      <c r="F154" t="str">
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B155" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B155" t="str">
+      <c r="C155" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace name should handle profile update for whitespace name</v>
       </c>
-      <c r="C155" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D155">
-        <v>201</v>
-      </c>
-      <c r="E155" t="str">
+      <c r="D155" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E155">
+        <v>212</v>
+      </c>
+      <c r="F155" t="str">
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
+        <v>Functional Test</v>
+      </c>
+      <c r="B156" t="str">
         <v>profile.spec.ts</v>
       </c>
-      <c r="B156" t="str">
+      <c r="C156" t="str">
         <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace bio should handle profile update for whitespace bio</v>
       </c>
-      <c r="C156" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D156">
-        <v>187</v>
-      </c>
-      <c r="E156" t="str">
+      <c r="D156" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E156">
+        <v>226</v>
+      </c>
+      <c r="F156" t="str">
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>freelancer-workflow.spec.ts</v>
+        <v>Functional Test</v>
       </c>
       <c r="B157" t="str">
-        <v>Freelancer Workflow (Empty State) should verify all buttons in empty state for freelancer</v>
+        <v>communication.spec.ts</v>
       </c>
       <c r="C157" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D157">
-        <v>2894</v>
-      </c>
-      <c r="E157" t="str">
+        <v>Communication should view messages page empty state</v>
+      </c>
+      <c r="D157" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E157">
+        <v>1606</v>
+      </c>
+      <c r="F157" t="str">
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>communication.spec.ts</v>
+        <v>Functional Test</v>
       </c>
       <c r="B158" t="str">
-        <v>Communication should view messages page empty state</v>
+        <v>freelancer-workflow.spec.ts</v>
       </c>
       <c r="C158" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D158">
-        <v>2743</v>
-      </c>
-      <c r="E158" t="str">
+        <v>Freelancer Workflow (Empty State) should verify all buttons in empty state for freelancer</v>
+      </c>
+      <c r="D158" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E158">
+        <v>3165</v>
+      </c>
+      <c r="F158" t="str">
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B159" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B159" t="str">
+      <c r="C159" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with variant: primary</v>
       </c>
-      <c r="C159" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D159">
-        <v>36</v>
-      </c>
-      <c r="E159" t="str">
+      <c r="D159" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E159">
+        <v>62</v>
+      </c>
+      <c r="F159" t="str">
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B160" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B160" t="str">
+      <c r="C160" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with variant: secondary</v>
       </c>
-      <c r="C160" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D160">
-        <v>6</v>
-      </c>
-      <c r="E160" t="str">
+      <c r="D160" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E160">
+        <v>4</v>
+      </c>
+      <c r="F160" t="str">
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B161" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B161" t="str">
+      <c r="C161" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with variant: outline</v>
       </c>
-      <c r="C161" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D161">
-        <v>4</v>
-      </c>
-      <c r="E161" t="str">
+      <c r="D161" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E161">
+        <v>3</v>
+      </c>
+      <c r="F161" t="str">
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B162" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B162" t="str">
+      <c r="C162" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with variant: ghost</v>
       </c>
-      <c r="C162" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D162">
+      <c r="D162" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E162">
         <v>3</v>
       </c>
-      <c r="E162" t="str">
+      <c r="F162" t="str">
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B163" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B163" t="str">
+      <c r="C163" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with size: sm</v>
       </c>
-      <c r="C163" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D163">
-        <v>3</v>
-      </c>
-      <c r="E163" t="str">
+      <c r="D163" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E163">
+        <v>5</v>
+      </c>
+      <c r="F163" t="str">
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B164" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B164" t="str">
+      <c r="C164" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with size: md</v>
       </c>
-      <c r="C164" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D164">
-        <v>2</v>
-      </c>
-      <c r="E164" t="str">
+      <c r="D164" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E164">
+        <v>5</v>
+      </c>
+      <c r="F164" t="str">
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B165" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B165" t="str">
+      <c r="C165" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders correctly with size: lg</v>
       </c>
-      <c r="C165" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D165">
-        <v>3</v>
-      </c>
-      <c r="E165" t="str">
+      <c r="D165" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E165">
+        <v>5</v>
+      </c>
+      <c r="F165" t="str">
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B166" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B166" t="str">
+      <c r="C166" t="str">
         <v>Unit Testing Core Components (20+ Cases) Button Component renders as disabled when disabled prop is true</v>
       </c>
-      <c r="C166" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D166">
-        <v>3</v>
-      </c>
-      <c r="E166" t="str">
+      <c r="D166" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E166">
+        <v>4</v>
+      </c>
+      <c r="F166" t="str">
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B167" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B167" t="str">
+      <c r="C167" t="str">
         <v>Unit Testing Core Components (20+ Cases) Sidebar Navigation renders all primary navigation links for unauthenticated state</v>
       </c>
-      <c r="C167" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D167">
-        <v>28</v>
-      </c>
-      <c r="E167" t="str">
+      <c r="D167" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E167">
+        <v>43</v>
+      </c>
+      <c r="F167" t="str">
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B168" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B168" t="str">
+      <c r="C168" t="str">
         <v>Unit Testing Core Components (20+ Cases) ForgotPassword Component renders email input and submit button</v>
       </c>
-      <c r="C168" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D168">
-        <v>61</v>
-      </c>
-      <c r="E168" t="str">
+      <c r="D168" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E168">
+        <v>75</v>
+      </c>
+      <c r="F168" t="str">
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B169" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B169" t="str">
+      <c r="C169" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 1] Formats currency correctly: 100 -&gt; $100.00</v>
       </c>
-      <c r="C169" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D169">
-        <v>17</v>
-      </c>
-      <c r="E169" t="str">
+      <c r="D169" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E169">
+        <v>29</v>
+      </c>
+      <c r="F169" t="str">
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B170" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B170" t="str">
+      <c r="C170" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 2] Formats currency correctly: 0 -&gt; $0.00</v>
       </c>
-      <c r="C170" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="E170" t="str">
+      <c r="D170" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170" t="str">
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B171" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B171" t="str">
+      <c r="C171" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 3] Formats currency correctly: -50 -&gt; -$50.00</v>
       </c>
-      <c r="C171" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="E171" t="str">
+      <c r="D171" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171" t="str">
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B172" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B172" t="str">
+      <c r="C172" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 4] Formats currency correctly: 1234.56 -&gt; $1,234.56</v>
       </c>
-      <c r="C172" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D172">
+      <c r="D172" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E172">
         <v>1</v>
       </c>
-      <c r="E172" t="str">
+      <c r="F172" t="str">
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B173" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B173" t="str">
+      <c r="C173" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 5] Formats currency correctly: 9999999 -&gt; $9,999,999.00</v>
       </c>
-      <c r="C173" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="E173" t="str">
+      <c r="D173" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173" t="str">
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B174" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B174" t="str">
+      <c r="C174" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 6] Truncates text correctly: Hello World -&gt; Hello World</v>
       </c>
-      <c r="C174" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="E174" t="str">
+      <c r="D174" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174" t="str">
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B175" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B175" t="str">
+      <c r="C175" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 7] Truncates text correctly: Hello World -&gt; Hello...</v>
       </c>
-      <c r="C175" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D175">
+      <c r="D175" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E175">
         <v>1</v>
       </c>
-      <c r="E175" t="str">
+      <c r="F175" t="str">
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
+        <v>Unit Test</v>
+      </c>
+      <c r="B176" t="str">
         <v>components.test.tsx</v>
       </c>
-      <c r="B176" t="str">
+      <c r="C176" t="str">
         <v>Utility Functions Testing (10+ Cases) [Utility 8] Truncates text correctly: A -&gt; A</v>
       </c>
-      <c r="C176" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176" t="str">
+      <c r="D176" t="str">
+        <v>passed</v>
+      </c>
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="F176" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F176"/>
   </ignoredErrors>
 </worksheet>
 </file>